--- a/research/traditional_assets/database/data/kuwait/kuwait_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_business_consumer_services.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00024</v>
+        <v>0.0155</v>
+      </c>
+      <c r="E2">
+        <v>0.47</v>
       </c>
       <c r="G2">
-        <v>-0.006605504587155963</v>
+        <v>0.1669811320754717</v>
       </c>
       <c r="H2">
-        <v>-0.006605504587155963</v>
+        <v>0.1669811320754717</v>
       </c>
       <c r="I2">
-        <v>-0.06724770642201834</v>
+        <v>-0.01669811320754717</v>
       </c>
       <c r="J2">
-        <v>-0.06724770642201834</v>
+        <v>-0.01669811320754717</v>
       </c>
       <c r="K2">
-        <v>2.32</v>
+        <v>3.43</v>
       </c>
       <c r="L2">
-        <v>0.2128440366972477</v>
+        <v>0.3235849056603774</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.279</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="V2">
-        <v>0.02196850393700788</v>
+        <v>0.00717948717948718</v>
       </c>
       <c r="W2">
-        <v>0.5110132158590308</v>
+        <v>0.4935251798561151</v>
       </c>
       <c r="X2">
-        <v>0.07272389500779955</v>
+        <v>0.1174316776575269</v>
       </c>
       <c r="Y2">
-        <v>0.4382893208512313</v>
+        <v>0.3760935021985883</v>
       </c>
       <c r="Z2">
-        <v>-6.404230317273796</v>
+        <v>12.45593419506462</v>
       </c>
       <c r="AA2">
-        <v>0.4306698002350176</v>
+        <v>-0.2079905992949469</v>
       </c>
       <c r="AB2">
-        <v>0.06493951393182208</v>
+        <v>0.1105754692161585</v>
       </c>
       <c r="AC2">
-        <v>0.3657302863031955</v>
+        <v>-0.3185660685111054</v>
       </c>
       <c r="AD2">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="AG2">
-        <v>2.461</v>
+        <v>1.336</v>
       </c>
       <c r="AH2">
-        <v>0.1774611398963731</v>
+        <v>0.1082317073170732</v>
       </c>
       <c r="AI2">
-        <v>0.282765737874097</v>
+        <v>0.1222030981067126</v>
       </c>
       <c r="AJ2">
-        <v>0.1623243849350307</v>
+        <v>0.1024854249769868</v>
       </c>
       <c r="AK2">
-        <v>0.2615024970778876</v>
+        <v>0.1158113730929265</v>
       </c>
       <c r="AL2">
-        <v>0.6929999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AM2">
-        <v>0.6929999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AN2">
-        <v>7.191601049868767</v>
+        <v>1.279279279279279</v>
       </c>
       <c r="AO2">
-        <v>-1.057720057720058</v>
+        <v>-0.2408163265306122</v>
       </c>
       <c r="AP2">
-        <v>6.459317585301838</v>
+        <v>1.203603603603603</v>
       </c>
       <c r="AQ2">
-        <v>-1.057720057720058</v>
+        <v>-0.2408163265306122</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00024</v>
+        <v>0.0155</v>
+      </c>
+      <c r="E3">
+        <v>0.47</v>
       </c>
       <c r="G3">
-        <v>-0.006605504587155963</v>
+        <v>0.1669811320754717</v>
       </c>
       <c r="H3">
-        <v>-0.006605504587155963</v>
+        <v>0.1669811320754717</v>
       </c>
       <c r="I3">
-        <v>-0.06724770642201834</v>
+        <v>-0.01669811320754717</v>
       </c>
       <c r="J3">
-        <v>-0.06724770642201834</v>
+        <v>-0.01669811320754717</v>
       </c>
       <c r="K3">
-        <v>2.32</v>
+        <v>3.43</v>
       </c>
       <c r="L3">
-        <v>0.2128440366972477</v>
+        <v>0.3235849056603774</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.279</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="V3">
-        <v>0.02196850393700788</v>
+        <v>0.00717948717948718</v>
       </c>
       <c r="W3">
-        <v>0.5110132158590308</v>
+        <v>0.4935251798561151</v>
       </c>
       <c r="X3">
-        <v>0.07272389500779955</v>
+        <v>0.1174316776575269</v>
       </c>
       <c r="Y3">
-        <v>0.4382893208512313</v>
+        <v>0.3760935021985883</v>
       </c>
       <c r="Z3">
-        <v>-6.404230317273796</v>
+        <v>12.45593419506462</v>
       </c>
       <c r="AA3">
-        <v>0.4306698002350176</v>
+        <v>-0.2079905992949469</v>
       </c>
       <c r="AB3">
-        <v>0.06493951393182208</v>
+        <v>0.1105754692161585</v>
       </c>
       <c r="AC3">
-        <v>0.3657302863031955</v>
+        <v>-0.3185660685111054</v>
       </c>
       <c r="AD3">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="AG3">
-        <v>2.461</v>
+        <v>1.336</v>
       </c>
       <c r="AH3">
-        <v>0.1774611398963731</v>
+        <v>0.1082317073170732</v>
       </c>
       <c r="AI3">
-        <v>0.282765737874097</v>
+        <v>0.1222030981067126</v>
       </c>
       <c r="AJ3">
-        <v>0.1623243849350307</v>
+        <v>0.1024854249769868</v>
       </c>
       <c r="AK3">
-        <v>0.2615024970778876</v>
+        <v>0.1158113730929265</v>
       </c>
       <c r="AL3">
-        <v>0.6929999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AM3">
-        <v>0.6929999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AN3">
-        <v>7.191601049868767</v>
+        <v>1.279279279279279</v>
       </c>
       <c r="AO3">
-        <v>-1.057720057720058</v>
+        <v>-0.2408163265306122</v>
       </c>
       <c r="AP3">
-        <v>6.459317585301838</v>
+        <v>1.203603603603603</v>
       </c>
       <c r="AQ3">
-        <v>-1.057720057720058</v>
+        <v>-0.2408163265306122</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_business_consumer_services.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0155</v>
-      </c>
-      <c r="E2">
-        <v>0.47</v>
+        <v>-0.0193</v>
       </c>
       <c r="G2">
-        <v>0.1669811320754717</v>
+        <v>-0.2528216704288939</v>
       </c>
       <c r="H2">
-        <v>0.1669811320754717</v>
+        <v>-0.2528216704288939</v>
       </c>
       <c r="I2">
-        <v>-0.01669811320754717</v>
+        <v>-0.371331828442438</v>
       </c>
       <c r="J2">
-        <v>-0.01669811320754717</v>
+        <v>-0.371331828442438</v>
       </c>
       <c r="K2">
-        <v>3.43</v>
+        <v>-4</v>
       </c>
       <c r="L2">
-        <v>0.3235849056603774</v>
+        <v>-0.4514672686230249</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.08400000000000001</v>
+        <v>0.285</v>
       </c>
       <c r="V2">
-        <v>0.00717948717948718</v>
+        <v>0.03877551020408163</v>
       </c>
       <c r="W2">
-        <v>0.4935251798561151</v>
+        <v>-0.3921568627450981</v>
       </c>
       <c r="X2">
-        <v>0.1174316776575269</v>
+        <v>0.102058634977763</v>
       </c>
       <c r="Y2">
-        <v>0.3760935021985883</v>
+        <v>-0.4942154977228611</v>
       </c>
       <c r="Z2">
-        <v>12.45593419506462</v>
+        <v>2.75497512437811</v>
       </c>
       <c r="AA2">
-        <v>-0.2079905992949469</v>
+        <v>-1.023009950248756</v>
       </c>
       <c r="AB2">
-        <v>0.1105754692161585</v>
+        <v>0.09339150862912154</v>
       </c>
       <c r="AC2">
-        <v>-0.3185660685111054</v>
+        <v>-1.116401458877878</v>
       </c>
       <c r="AD2">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AG2">
-        <v>1.336</v>
+        <v>1.255</v>
       </c>
       <c r="AH2">
-        <v>0.1082317073170732</v>
+        <v>0.1732283464566929</v>
       </c>
       <c r="AI2">
-        <v>0.1222030981067126</v>
+        <v>0.1984536082474227</v>
       </c>
       <c r="AJ2">
-        <v>0.1024854249769868</v>
+        <v>0.1458454386984311</v>
       </c>
       <c r="AK2">
-        <v>0.1158113730929265</v>
+        <v>0.1678929765886288</v>
       </c>
       <c r="AL2">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AN2">
-        <v>1.279279279279279</v>
+        <v>-0.4502923976608187</v>
       </c>
       <c r="AO2">
-        <v>-0.2408163265306122</v>
+        <v>-3.496280552603614</v>
       </c>
       <c r="AP2">
-        <v>1.203603603603603</v>
+        <v>-0.3669590643274854</v>
       </c>
       <c r="AQ2">
-        <v>-0.2408163265306122</v>
+        <v>-3.496280552603614</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0155</v>
-      </c>
-      <c r="E3">
-        <v>0.47</v>
+        <v>-0.0193</v>
       </c>
       <c r="G3">
-        <v>0.1669811320754717</v>
+        <v>-0.2528216704288939</v>
       </c>
       <c r="H3">
-        <v>0.1669811320754717</v>
+        <v>-0.2528216704288939</v>
       </c>
       <c r="I3">
-        <v>-0.01669811320754717</v>
+        <v>-0.371331828442438</v>
       </c>
       <c r="J3">
-        <v>-0.01669811320754717</v>
+        <v>-0.371331828442438</v>
       </c>
       <c r="K3">
-        <v>3.43</v>
+        <v>-4</v>
       </c>
       <c r="L3">
-        <v>0.3235849056603774</v>
+        <v>-0.4514672686230249</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.08400000000000001</v>
+        <v>0.285</v>
       </c>
       <c r="V3">
-        <v>0.00717948717948718</v>
+        <v>0.03877551020408163</v>
       </c>
       <c r="W3">
-        <v>0.4935251798561151</v>
+        <v>-0.3921568627450981</v>
       </c>
       <c r="X3">
-        <v>0.1174316776575269</v>
+        <v>0.102058634977763</v>
       </c>
       <c r="Y3">
-        <v>0.3760935021985883</v>
+        <v>-0.4942154977228611</v>
       </c>
       <c r="Z3">
-        <v>12.45593419506462</v>
+        <v>2.75497512437811</v>
       </c>
       <c r="AA3">
-        <v>-0.2079905992949469</v>
+        <v>-1.023009950248756</v>
       </c>
       <c r="AB3">
-        <v>0.1105754692161585</v>
+        <v>0.09339150862912154</v>
       </c>
       <c r="AC3">
-        <v>-0.3185660685111054</v>
+        <v>-1.116401458877878</v>
       </c>
       <c r="AD3">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AG3">
-        <v>1.336</v>
+        <v>1.255</v>
       </c>
       <c r="AH3">
-        <v>0.1082317073170732</v>
+        <v>0.1732283464566929</v>
       </c>
       <c r="AI3">
-        <v>0.1222030981067126</v>
+        <v>0.1984536082474227</v>
       </c>
       <c r="AJ3">
-        <v>0.1024854249769868</v>
+        <v>0.1458454386984311</v>
       </c>
       <c r="AK3">
-        <v>0.1158113730929265</v>
+        <v>0.1678929765886288</v>
       </c>
       <c r="AL3">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AM3">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AN3">
-        <v>1.279279279279279</v>
+        <v>-0.4502923976608187</v>
       </c>
       <c r="AO3">
-        <v>-0.2408163265306122</v>
+        <v>-3.496280552603614</v>
       </c>
       <c r="AP3">
-        <v>1.203603603603603</v>
+        <v>-0.3669590643274854</v>
       </c>
       <c r="AQ3">
-        <v>-0.2408163265306122</v>
+        <v>-3.496280552603614</v>
       </c>
     </row>
   </sheetData>
